--- a/SuppXLS/Scen_RES_SHARE_90%_24_7.xlsx
+++ b/SuppXLS/Scen_RES_SHARE_90%_24_7.xlsx
@@ -4408,7 +4408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B3:H5"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.140625" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -4419,6 +4419,8 @@
     <col width="10.7109375" bestFit="1" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1"/>
+    <row r="2"/>
     <row r="3">
       <c r="B3" s="3" t="inlineStr">
         <is>
@@ -4464,11 +4466,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>DAYNITE</t>
-        </is>
-      </c>
+      <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>ELC_FIN_DEM</t>
@@ -4484,10 +4482,8 @@
           <t>FLO_SHAR</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2030,2035,2040,2045,2050</t>
-        </is>
+      <c r="F5" s="2" t="n">
+        <v>2030</v>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
@@ -4498,6 +4494,118 @@
         <v>0.9</v>
       </c>
     </row>
+    <row r="6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ELC_FIN_DEM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ELC_GRID_RES</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>FLO_SHAR</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>2035</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LO</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ELC_FIN_DEM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ELC_GRID_RES</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>FLO_SHAR</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LO</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ELC_FIN_DEM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ELC_GRID_RES</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>FLO_SHAR</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>2045</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>LO</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ELC_FIN_DEM</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ELC_GRID_RES</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>FLO_SHAR</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>2050</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>LO</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
